--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,108 +14,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+  <x:si>
+    <x:t>프리셋 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap3</x:t>
+  </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap3</x:t>
   </x:si>
   <x:si>
-    <x:t>프리셋 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/ArrivePortal</x:t>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap2</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/BasicMap5</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap4</x:t>
+    <x:t>Prefabs/Map/PresetMap4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -270,6 +279,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -352,6 +362,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -386,6 +397,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -430,6 +442,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -473,6 +486,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -557,26 +571,28 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -607,6 +623,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1307,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I12"/>
+  <x:dimension ref="A1:I13"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1322,13 +1339,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1338,13 +1355,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1355,13 +1372,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1371,13 +1388,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1386,13 +1403,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1401,10 +1418,10 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
         <x:v>28</x:v>
@@ -1416,44 +1433,44 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:3" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
         <x:v>33</x:v>
@@ -1461,24 +1478,35 @@
     </x:row>
     <x:row r="11" spans="1:3" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3" customHeight="1">
+      <x:c r="A13" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,117 +14,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+  <x:si>
+    <x:t>기본 맵 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
   <x:si>
     <x:t>프리셋 맵 4</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵 3</x:t>
+    <x:t>프리셋 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 3</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>프리셋 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 2</x:t>
+    <x:t>기본 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵 4</x:t>
+    <x:t>프리팹 경로</x:t>
   </x:si>
   <x:si>
     <x:t>기본 맵 2</x:t>
   </x:si>
   <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
+    <x:t>기본 맵 5</x:t>
   </x:si>
   <x:si>
     <x:t>맵 이름</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵 5</x:t>
+    <x:t>아이디</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
     <x:t>도착지</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefabs/Map/PresetMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
     <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/ArrivePortal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -279,7 +297,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -362,7 +379,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -397,7 +413,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -442,7 +457,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -486,7 +500,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -571,28 +584,26 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -623,7 +634,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1324,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I13"/>
+  <x:dimension ref="A1:I15"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1339,13 +1349,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1355,13 +1365,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1372,13 +1382,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1388,13 +1398,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1403,13 +1413,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1418,13 +1428,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1433,80 +1443,102 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:3" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3" customHeight="1">
+      <x:c r="A14" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3" customHeight="1">
+      <x:c r="A15" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>36</x:v>
+      <x:c r="C15" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,135 +14,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+  <x:si>
+    <x:t>프리셋 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
   <x:si>
     <x:t>기본 맵 7</x:t>
   </x:si>
   <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
     <x:t>기본 맵 6</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Preset_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
+    <x:t>맵 이름</x:t>
   </x:si>
   <x:si>
     <x:t>프리셋 맵 4</x:t>
   </x:si>
   <x:si>
-    <x:t>프리셋 맵 2</x:t>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 4</x:t>
   </x:si>
   <x:si>
     <x:t>프리셋 맵 3</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>프리팹 경로</x:t>
   </x:si>
   <x:si>
     <x:t>기본 맵 2</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap7</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap3</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
+    <x:t>Prefabs/Map/BasicMap5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/BasicMap2</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/PresetMap4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap5</x:t>
-  </x:si>
-  <x:si>
     <x:t>Prefabs/Map/BasicMap4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/ArrivePortal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -297,6 +306,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -379,6 +389,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -413,6 +424,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -457,6 +469,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -500,6 +513,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -584,26 +598,28 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -634,6 +650,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1334,7 +1351,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I15"/>
+  <x:dimension ref="A1:I16"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1349,13 +1366,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1365,13 +1382,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1382,13 +1399,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1401,10 +1418,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1413,13 +1430,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1428,13 +1445,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1443,80 +1460,80 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:3" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3" customHeight="1">
@@ -1524,10 +1541,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3" customHeight="1">
@@ -1535,10 +1552,21 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3" customHeight="1">
+      <x:c r="A16" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C15" s="2" t="s">
-        <x:v>39</x:v>
+      <x:c r="C16" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/MapData.xlsx
+++ b/JsonConverter/ExcelFiles/MapData.xlsx
@@ -14,144 +14,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+  <x:si>
+    <x:t>기본 맵 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리셋 맵 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맵 이름</x:t>
+  </x:si>
   <x:si>
     <x:t>프리셋 맵 5</x:t>
   </x:si>
   <x:si>
+    <x:t>기본 맵 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 맵 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/ArrivePortal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Portal_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Basic_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map_Preset_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>Map_Preset_05</x:t>
   </x:si>
   <x:si>
-    <x:t>Map_Preset_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Portal_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Preset_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map_Basic_06</x:t>
-  </x:si>
-  <x:si>
     <x:t>Map_Basic_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도착지</x:t>
+    <x:t>Prefabs/Map/BasicMap6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/PresetMap1</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Map/PresetMap5</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 맵 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맵 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리셋 맵 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 맵 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/ArrivePortal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap4</x:t>
-  </x:si>
-  <x:si>
     <x:t>Prefabs/Map/BasicMap3</x:t>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Map/BasicMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/PresetMap1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Map/BasicMap4</x:t>
+    <x:t>Prefabs/Map/BasicMap10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Map/BasicMap8</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -274,7 +301,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -295,6 +322,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -306,7 +336,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -389,7 +418,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -424,7 +452,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -469,7 +496,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -513,7 +539,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -598,28 +623,26 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -650,7 +673,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1351,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I16"/>
+  <x:dimension ref="A1:I19"/>
   <x:sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -1366,13 +1388,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1382,13 +1404,13 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
@@ -1399,13 +1421,13 @@
     </x:row>
     <x:row r="3" spans="1:8" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
@@ -1415,13 +1437,13 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
@@ -1430,13 +1452,13 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
@@ -1445,13 +1467,13 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
@@ -1460,113 +1482,146 @@
     </x:row>
     <x:row r="7" spans="1:3" customHeight="1">
       <x:c r="A7" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:3" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3" customHeight="1">
+      <x:c r="A17" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3" customHeight="1">
+      <x:c r="A18" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="C18" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3" customHeight="1">
+      <x:c r="A19" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="s">
         <x:v>17</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
